--- a/exports/IOC_full_report.xlsx
+++ b/exports/IOC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>62.63</v>
+        <v>61.87</v>
       </c>
       <c r="I2" t="n">
         <v>62.22103490798589</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.09</v>
+        <v>0.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.76</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>63.73</v>
+        <v>65.25</v>
       </c>
       <c r="I3" t="n">
         <v>65.18247375246507</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.01</v>
+        <v>-5.46</v>
       </c>
       <c r="L3" t="n">
-        <v>3.62</v>
+        <v>6.98</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="N3" t="n">
         <v>1.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.12</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>63.06</v>
+        <v>61.3</v>
       </c>
       <c r="I4" t="n">
         <v>61.5187854415162</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.36</v>
+        <v>-6.05</v>
       </c>
       <c r="L4" t="n">
         <v>7.51</v>
@@ -669,7 +716,7 @@
         <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>3.37</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>59.88</v>
+        <v>62.45</v>
       </c>
       <c r="I5" t="n">
         <v>60.56887045375997</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>-1.88</v>
       </c>
       <c r="L5" t="n">
         <v>4.73</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>70.8</v>
+        <v>66.91</v>
       </c>
       <c r="I6" t="n">
         <v>66.97878034154951</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K6" t="n">
-        <v>13.37</v>
+        <v>7.14</v>
       </c>
       <c r="L6" t="n">
         <v>5.11</v>
       </c>
       <c r="M6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>5.76</v>
       </c>
       <c r="O6" t="n">
         <v>3.96</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>54.51</v>
+        <v>55.32</v>
       </c>
       <c r="I7" t="n">
         <v>54.75090380978758</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>18.53</v>
+        <v>17.32</v>
       </c>
       <c r="L7" t="n">
         <v>4.47</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.62</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44754.38541666666</v>
+        <v>44754.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>53.37</v>
+        <v>52.85</v>
       </c>
       <c r="I8" t="n">
         <v>53.19345634498184</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.52</v>
+        <v>-4.46</v>
       </c>
       <c r="L8" t="n">
-        <v>3.69</v>
+        <v>4.88</v>
       </c>
       <c r="M8" t="n">
         <v>0.27</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44778.38541666666</v>
+        <v>44778.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>54.33</v>
+        <v>55.08</v>
       </c>
       <c r="I9" t="n">
         <v>54.90359618169953</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.8</v>
+        <v>-4.22</v>
       </c>
       <c r="L9" t="n">
         <v>4.67</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>5.05</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44796.55208333334</v>
+        <v>44797.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>53.33</v>
+        <v>52.75</v>
       </c>
       <c r="I10" t="n">
         <v>53.11891173577519</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.18</v>
+        <v>-4.23</v>
       </c>
       <c r="L10" t="n">
-        <v>4.05</v>
+        <v>4.32</v>
       </c>
       <c r="M10" t="n">
         <v>2.16</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.83</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44812.38541666666</v>
+        <v>44812.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>54.42</v>
+        <v>55.08</v>
       </c>
       <c r="I11" t="n">
         <v>54.71414288182532</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.17</v>
+        <v>-4.42</v>
       </c>
       <c r="L11" t="n">
-        <v>4.23</v>
+        <v>5.78</v>
       </c>
       <c r="M11" t="n">
         <v>0.8100000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>3.96</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>53.66</v>
+        <v>52.62</v>
       </c>
       <c r="I12" t="n">
         <v>52.90071154361389</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.58</v>
+        <v>-4.47</v>
       </c>
       <c r="L12" t="n">
-        <v>2.92</v>
+        <v>4.56</v>
       </c>
       <c r="M12" t="n">
         <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>0.85</v>
+        <v>2.93</v>
       </c>
       <c r="O12" t="n">
         <v>2.65</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.24</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>49.76</v>
+        <v>50.39</v>
       </c>
       <c r="I13" t="n">
         <v>50.34402694843543</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>5.44</v>
+        <v>4.24</v>
       </c>
       <c r="L13" t="n">
         <v>2.34</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.29</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>58.22</v>
+        <v>57.08</v>
       </c>
       <c r="I14" t="n">
         <v>57.29775748300661</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>15.54</v>
+        <v>13.28</v>
       </c>
       <c r="L14" t="n">
         <v>4.72</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.53</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>56.98</v>
+        <v>58.97</v>
       </c>
       <c r="I15" t="n">
         <v>58.37991819251931</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18</v>
+        <v>-3.31</v>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>3.99</v>
       </c>
       <c r="M15" t="n">
         <v>0.49</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>6.26</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>64.44</v>
+        <v>62.07</v>
       </c>
       <c r="I16" t="n">
         <v>62.33517244041292</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>9.279999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="L16" t="n">
         <v>3.04</v>
       </c>
       <c r="M16" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="N16" t="n">
         <v>2.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.08</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>59.97</v>
+        <v>61.35</v>
       </c>
       <c r="I17" t="n">
         <v>60.46028620809253</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K17" t="n">
-        <v>3.38</v>
+        <v>1.16</v>
       </c>
       <c r="L17" t="n">
         <v>4.12</v>
@@ -1410,7 +1613,7 @@
         <v>0.92</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
         <v>-2.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45012.38541666666</v>
+        <v>45012.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>59.5</v>
+        <v>58.84</v>
       </c>
       <c r="I18" t="n">
         <v>59.19930413911715</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.02</v>
+        <v>-4.09</v>
       </c>
       <c r="L18" t="n">
-        <v>3.63</v>
+        <v>4.42</v>
       </c>
       <c r="M18" t="n">
         <v>0.95</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>4.85</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45042.55208333334</v>
+        <v>45043.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>60.26</v>
+        <v>61.97</v>
       </c>
       <c r="I19" t="n">
         <v>60.83320379475744</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.41</v>
+        <v>-5.32</v>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
         <v>0.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>3.22</v>
       </c>
       <c r="O19" t="n">
         <v>-1.97</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.59</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>72.23</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>71.48825653528196</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>16.56</v>
+        <v>13.88</v>
       </c>
       <c r="L20" t="n">
         <v>2.61</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.12</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>72.42</v>
+        <v>75.98</v>
       </c>
       <c r="I21" t="n">
         <v>73.34478792478201</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.62</v>
+        <v>-7.67</v>
       </c>
       <c r="L21" t="n">
-        <v>3.56</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="N21" t="n">
-        <v>2.09</v>
+        <v>5.83</v>
       </c>
       <c r="O21" t="n">
         <v>-3.69</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>77.87</v>
+        <v>77.59</v>
       </c>
       <c r="I22" t="n">
         <v>77.70302091610407</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="L22" t="n">
         <v>4.63</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.94</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45175.55208333334</v>
+        <v>45176.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>75.45999999999999</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>75.70915569817913</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K23" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="L23" t="n">
         <v>1.16</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>3.69</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>75.98</v>
+        <v>75.64</v>
       </c>
       <c r="I24" t="n">
         <v>75.65467133711054</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>0.32</v>
+        <v>-0.13</v>
       </c>
       <c r="L24" t="n">
         <v>0.87</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>4.16</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.45</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45211.38541666666</v>
+        <v>45211.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>74.18000000000001</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>74.48851161332179</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="L25" t="n">
         <v>4.34</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>3.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>74.31</v>
+        <v>72.7</v>
       </c>
       <c r="I26" t="n">
         <v>73.26312418976462</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.27</v>
+        <v>-2.43</v>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>0.82</v>
       </c>
       <c r="N26" t="n">
-        <v>1.12</v>
+        <v>2.49</v>
       </c>
       <c r="O26" t="n">
         <v>0.98</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45230.38541666666</v>
+        <v>45230.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>72.03</v>
+        <v>74.08</v>
       </c>
       <c r="I27" t="n">
         <v>73.67407617888654</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>0.92</v>
+        <v>-1.9</v>
       </c>
       <c r="L27" t="n">
         <v>2.28</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.48</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>127.26</v>
+        <v>125.93</v>
       </c>
       <c r="I28" t="n">
         <v>126.695417142393</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>83.83333333333333</v>
+        <v>84</v>
       </c>
       <c r="K28" t="n">
-        <v>71.79000000000001</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>2.88</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>135.71</v>
+        <v>147.31</v>
       </c>
       <c r="I29" t="n">
         <v>136.1606359031955</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.77</v>
+        <v>-16.98</v>
       </c>
       <c r="L29" t="n">
-        <v>9.51</v>
+        <v>18.26</v>
       </c>
       <c r="M29" t="n">
         <v>1.24</v>
       </c>
       <c r="N29" t="n">
-        <v>3.47</v>
+        <v>9.31</v>
       </c>
       <c r="O29" t="n">
         <v>-6.29</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>161.65</v>
+        <v>159.55</v>
       </c>
       <c r="I30" t="n">
         <v>160.5643949547151</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>9.73</v>
+        <v>8.31</v>
       </c>
       <c r="L30" t="n">
         <v>7.13</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.01</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>154.19</v>
+        <v>156.94</v>
       </c>
       <c r="I31" t="n">
         <v>156.7749327618379</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>3.36</v>
+        <v>1.64</v>
       </c>
       <c r="L31" t="n">
         <v>11.37</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.79</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>155.61</v>
+        <v>151.1</v>
       </c>
       <c r="I32" t="n">
         <v>153.1798326834663</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.85</v>
+        <v>-3.72</v>
       </c>
       <c r="L32" t="n">
         <v>6.09</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>153</v>
+        <v>154.71</v>
       </c>
       <c r="I33" t="n">
         <v>153.60224016877</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.26</v>
+        <v>-2.39</v>
       </c>
       <c r="L33" t="n">
         <v>3.71</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>5.55</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>160.03</v>
+        <v>143.41</v>
       </c>
       <c r="I34" t="n">
         <v>149.8678421070928</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K34" t="n">
-        <v>3.44</v>
+        <v>-7.3</v>
       </c>
       <c r="L34" t="n">
-        <v>5.43</v>
+        <v>12.83</v>
       </c>
       <c r="M34" t="n">
         <v>0.41</v>
       </c>
       <c r="N34" t="n">
-        <v>1.68</v>
+        <v>12.14</v>
       </c>
       <c r="O34" t="n">
         <v>0.37</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.98</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45476.55208333334</v>
+        <v>45477.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>153.95</v>
+        <v>154.56</v>
       </c>
       <c r="I35" t="n">
         <v>154.384774021287</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.35</v>
+        <v>-7.77</v>
       </c>
       <c r="L35" t="n">
         <v>12.58</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>3.3</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>168.03</v>
+        <v>161.45</v>
       </c>
       <c r="I36" t="n">
         <v>162.6773348366152</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K36" t="n">
-        <v>8.720000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="L36" t="n">
         <v>1.56</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
         <v>0.82</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>163.35</v>
+        <v>164.94</v>
       </c>
       <c r="I37" t="n">
         <v>164.1613807852721</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.18</v>
+        <v>-2.16</v>
       </c>
       <c r="L37" t="n">
         <v>2.87</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>4.78</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45545.55208333334</v>
+        <v>45546.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>166.75</v>
+        <v>163.28</v>
       </c>
       <c r="I38" t="n">
         <v>164.979690259997</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>1.1</v>
+        <v>-1.01</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
         <v>0.57</v>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>3.12</v>
       </c>
       <c r="O38" t="n">
         <v>1.11</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.93</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>162.88</v>
+        <v>169</v>
       </c>
       <c r="I39" t="n">
         <v>164.2271957385965</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>0.24</v>
+        <v>-3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
         <v>0.82</v>
       </c>
       <c r="N39" t="n">
-        <v>1.83</v>
+        <v>4.46</v>
       </c>
       <c r="O39" t="n">
         <v>-3.12</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.21</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45568.38541666666</v>
+        <v>45568.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>162.96</v>
+        <v>162.39</v>
       </c>
       <c r="I40" t="n">
         <v>162.8218691662058</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.57</v>
+        <v>-3.91</v>
       </c>
       <c r="L40" t="n">
-        <v>3.62</v>
+        <v>4.06</v>
       </c>
       <c r="M40" t="n">
         <v>3.23</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.91</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45623.38541666666</v>
+        <v>45623.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>129.69</v>
+        <v>132.22</v>
       </c>
       <c r="I41" t="n">
         <v>131.4772772744922</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>54.83333333333334</v>
+        <v>55</v>
       </c>
       <c r="K41" t="n">
-        <v>20.14</v>
+        <v>18.58</v>
       </c>
       <c r="L41" t="n">
         <v>0.57</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.88</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>133.15</v>
+        <v>130.54</v>
       </c>
       <c r="I42" t="n">
         <v>131.3627850890863</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7</v>
+        <v>-1.27</v>
       </c>
       <c r="L42" t="n">
         <v>1.92</v>
@@ -2835,7 +3338,7 @@
         <v>0.87</v>
       </c>
       <c r="N42" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O42" t="n">
         <v>1.75</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45677.38541666666</v>
+        <v>45677.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>122.99</v>
+        <v>124.01</v>
       </c>
       <c r="I43" t="n">
         <v>123.7589915698885</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>5.78</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>3.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>120.67</v>
+        <v>117.76</v>
       </c>
       <c r="I44" t="n">
         <v>119.2540621327634</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.69</v>
+        <v>-5.04</v>
       </c>
       <c r="L44" t="n">
-        <v>4.1</v>
+        <v>6.18</v>
       </c>
       <c r="M44" t="n">
         <v>0.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.87</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>112.12</v>
+        <v>115.15</v>
       </c>
       <c r="I45" t="n">
         <v>112.951540168872</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>4.79</v>
+        <v>2.22</v>
       </c>
       <c r="L45" t="n">
         <v>4.64</v>
@@ -3006,7 +3545,7 @@
         <v>1.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.02</v>
+        <v>3.59</v>
       </c>
       <c r="O45" t="n">
         <v>-3.43</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.42</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>132.97</v>
+        <v>132.6</v>
       </c>
       <c r="I46" t="n">
         <v>132.8142666087625</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K46" t="n">
-        <v>15.48</v>
+        <v>15.15</v>
       </c>
       <c r="L46" t="n">
         <v>2.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>134.95</v>
+        <v>138.65</v>
       </c>
       <c r="I47" t="n">
         <v>137.4224473217564</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.77</v>
+        <v>-4.56</v>
       </c>
       <c r="L47" t="n">
-        <v>5.18</v>
+        <v>5.43</v>
       </c>
       <c r="M47" t="n">
         <v>2.76</v>
       </c>
       <c r="N47" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="O47" t="n">
         <v>0.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>134.53</v>
+        <v>133.01</v>
       </c>
       <c r="I48" t="n">
         <v>133.1217499074315</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.97</v>
+        <v>-4.07</v>
       </c>
       <c r="L48" t="n">
         <v>6.15</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.19</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>134.95</v>
+        <v>137.39</v>
       </c>
       <c r="I49" t="n">
         <v>136.8152289795746</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.46</v>
+        <v>-3.29</v>
       </c>
       <c r="L49" t="n">
         <v>3.74</v>
@@ -3234,7 +3821,7 @@
         <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>-0.61</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>141.34</v>
+        <v>139.66</v>
       </c>
       <c r="I50" t="n">
         <v>140.9046889339153</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="L50" t="n">
         <v>1.83</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.11</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>137</v>
+        <v>139.86</v>
       </c>
       <c r="I51" t="n">
         <v>137.5337059283558</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>1.9</v>
+        <v>-0.14</v>
       </c>
       <c r="L51" t="n">
         <v>2.13</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>3.96</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>161.69</v>
+        <v>161.08</v>
       </c>
       <c r="I52" t="n">
         <v>161.4884304056202</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K52" t="n">
-        <v>15.61</v>
+        <v>15.17</v>
       </c>
       <c r="L52" t="n">
         <v>2.27</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.09</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>158.97</v>
+        <v>162.2</v>
       </c>
       <c r="I53" t="n">
         <v>161.8045739944872</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>1.31</v>
+        <v>-0.7</v>
       </c>
       <c r="L53" t="n">
         <v>1.08</v>
       </c>
       <c r="M53" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>1.26</v>
+        <v>3.15</v>
       </c>
       <c r="O53" t="n">
         <v>-0.63</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.58</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>162.5</v>
+        <v>157.06</v>
       </c>
       <c r="I54" t="n">
         <v>160.5388001098009</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>0.18</v>
+        <v>-3.17</v>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>3.21</v>
       </c>
       <c r="M54" t="n">
         <v>0.74</v>
       </c>
       <c r="N54" t="n">
-        <v>1.27</v>
+        <v>3.85</v>
       </c>
       <c r="O54" t="n">
         <v>3.15</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.64</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46055.38541666666</v>
+        <v>46055.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>161.52</v>
+        <v>164.88</v>
       </c>
       <c r="I55" t="n">
         <v>163.3289335404914</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.84</v>
+        <v>-4.98</v>
       </c>
       <c r="L55" t="n">
-        <v>4.83</v>
+        <v>5.31</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>187</v>
+        <v>178.24</v>
       </c>
       <c r="I56" t="n">
         <v>180.109897949232</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>13.42</v>
+        <v>8.1</v>
       </c>
       <c r="L56" t="n">
         <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>0.51</v>
+        <v>3.04</v>
       </c>
       <c r="N56" t="n">
-        <v>2.69</v>
+        <v>4.24</v>
       </c>
       <c r="O56" t="n">
         <v>3.3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>6.55</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>134.7</v>
+        <v>143.55</v>
       </c>
       <c r="I57" t="n">
         <v>142.7713697209854</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>24.43</v>
+        <v>19.46</v>
       </c>
       <c r="L57" t="n">
         <v>2.33</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>6.16</v>
       </c>
       <c r="N57" t="n">
-        <v>1.25</v>
+        <v>6.6</v>
       </c>
       <c r="O57" t="n">
         <v>-4.24</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.77</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>141.28</v>
+        <v>140.3</v>
       </c>
       <c r="I58" t="n">
         <v>141.1309690380249</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.58</v>
+        <v>-2.26</v>
       </c>
       <c r="L58" t="n">
         <v>4.17</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.06</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>138.24</v>
+        <v>140.21</v>
       </c>
       <c r="I59" t="n">
         <v>139.3978411329516</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K59" t="n">
-        <v>1.47</v>
+        <v>0.06</v>
       </c>
       <c r="L59" t="n">
         <v>1.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.37</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>138.95</v>
+        <v>137.49</v>
       </c>
       <c r="I60" t="n">
         <v>137.6118801796554</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.9</v>
+        <v>-1.94</v>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>2.57</v>
       </c>
       <c r="M60" t="n">
         <v>0.6</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.03</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>137.24</v>
+        <v>141.2</v>
       </c>
       <c r="I61" t="n">
         <v>140.1239562754291</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>0.18</v>
+        <v>-2.7</v>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>2.88</v>
       </c>
       <c r="M61" t="n">
         <v>1.78</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.48</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>143.94</v>
+        <v>139.67</v>
       </c>
       <c r="I62" t="n">
         <v>140.0154020032662</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>1.94</v>
+        <v>-1.08</v>
       </c>
       <c r="L62" t="n">
         <v>2.9</v>
@@ -3975,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="O62" t="n">
         <v>4.9</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.37</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46223.55208333334</v>
+        <v>46224.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>142.6</v>
+        <v>143.7</v>
       </c>
       <c r="I63" t="n">
         <v>142.8609034730563</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.1</v>
+        <v>-2.89</v>
       </c>
       <c r="L63" t="n">
         <v>3.18</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.54</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>139.1</v>
+        <v>138.08</v>
       </c>
       <c r="I64" t="n">
         <v>138.4746391334447</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.2</v>
+        <v>-3.91</v>
       </c>
       <c r="L64" t="n">
         <v>4.82</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>137.2</v>
+        <v>137.96</v>
       </c>
       <c r="I65" t="n">
         <v>137.6243224374704</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n">
-        <v>0.64</v>
+        <v>0.09</v>
       </c>
       <c r="L65" t="n">
         <v>2.22</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>2.95</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>135.86</v>
+        <v>133.48</v>
       </c>
       <c r="I66" t="n">
         <v>133.8889868667704</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.52</v>
+        <v>-3.25</v>
       </c>
       <c r="L66" t="n">
-        <v>1.91</v>
+        <v>3.38</v>
       </c>
       <c r="M66" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>1.16</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
         <v>0.18</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>3.93</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>130</v>
+        <v>131.12</v>
       </c>
       <c r="I67" t="n">
         <v>130.5467421230372</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K67" t="n">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="L67" t="n">
         <v>1.88</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,12 @@
       <c r="Q68" t="n">
         <v>2</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6422,7 +7243,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.4</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -6432,7 +7253,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -6442,7 +7263,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6452,7 +7273,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -6462,7 +7283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -6472,7 +7293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="11">
@@ -6482,7 +7303,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6492,7 +7313,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6502,7 +7323,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="14">
@@ -6512,7 +7333,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.55</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="15">
@@ -6522,7 +7343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.19</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="16">
@@ -6532,7 +7353,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="17">
@@ -6542,7 +7363,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71.79000000000001</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6552,7 +7373,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="19">
@@ -6562,7 +7383,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.65</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="20">
@@ -6572,7 +7393,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="21">
@@ -6582,7 +7403,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.58</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="22">
@@ -6592,7 +7413,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -6602,7 +7423,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6612,7 +7433,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="25">
@@ -6622,7 +7443,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.13</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="26">
@@ -6632,7 +7453,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.72</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="27">
@@ -6642,7 +7463,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.29</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="28">
@@ -6652,7 +7473,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
